--- a/oportunidades_obras_mt.xlsx
+++ b/oportunidades_obras_mt.xlsx
@@ -413,66 +413,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Categoria</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Município</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Prioritária (Cuiabá/VG)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Valor Estimado (R$)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Modalidade</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Data Publicação</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Encerramento Proposta</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>Órgão</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Município</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Prioritária (Cuiabá/VG)</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Categoria</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Modalidade</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Valor Estimado (R$)</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Data Publicação</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Objeto</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
         <is>
           <t>Processo</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Objeto</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Link PNCP</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Origem</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Alimentador</t>
         </is>
@@ -481,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PRIVADO: AGROPECUÁRIA &amp; LOGÍSTICA PANTANAL LTDA</t>
+          <t>Construção Civil</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -494,54 +499,55 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Construção Civil</t>
-        </is>
+      <c r="D2" t="n">
+        <v>50736684.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Alvará de Obra Privada (Galpão Logístico e Escritório Comercial)</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>2252500</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
+          <t>Dispensa</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ALV-CBA-2026/1842</t>
+          <t>DNIT-DEPARTAMENTO NACIONAL DE INFRAEST DE TRANSPORTES</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>[Distrito Industrial] Construção de barracão metálico para armazenagem e bloco administrativo de alvenaria. Área total aprovada: 850,00 m². Local: Av. A, Distrito Industrial, Cuiabá-MT.</t>
+          <t>Execução de Construção de Pontes e Obras de Arte Especiais na Rodovia BR-158/MT, Trecho: Divisa PA/MT - Divisa MT-GO, sub-trecho: Entr. BR-158 (Posto Luisinho) - Entr. BR-158 (Alô Brasil) (Contorno Leste da Reserva Indígena Marãiwatsédé - Lote A), Segmento: km 0,00 - km 93,99, extensão: 93,99 km - Trecho Planejado,  Código SNV: 158CMT1005; 158CMT1010; 158CMT1015; 158CMT1020.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>https://gazetamunicipal.cuiaba.mt.gov.br/</t>
+          <t>50611.000978/2024-37</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>🏗️ Obra Privada (Alvará)</t>
+          <t>https://pncp.gov.br/app/editais/04892707002235/2026/40</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Diário Oficial (Alvarás Cuiabá/VG)</t>
+          <t>🏛️ Governo / PNCP</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>PNCP / Compras.gov (Governo)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PRIVADO: CLÍNICA INTEGRADA SANTA ROSA EIRELI</t>
+          <t>Construção Civil</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -554,45 +560,46 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Reforma / Adequação Predial</t>
-        </is>
+      <c r="D3" t="n">
+        <v>2252500</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Alvará de Obra Privada (Reforma Comercial com Acréscimo de Área)</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>381600</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
+          <t>Alvará de Obra Privada (Galpão Logístico e Escritório Comercial)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ALV-CBA-2026/1790</t>
+          <t>PRIVADO: AGROPECUÁRIA &amp; LOGÍSTICA PANTANAL LTDA</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>[Bairro Santa Rosa] Reforma comercial com adequação de acessibilidade, consultórios médicos e reforço estrutural. Área total: 320,00 m². Local: Rua das Violetas, Santa Rosa, Cuiabá-MT.</t>
+          <t>[Distrito Industrial] Construção de barracão metálico para armazenagem e bloco administrativo de alvenaria. Área total aprovada: 850,00 m². Local: Av. A, Distrito Industrial, Cuiabá-MT.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>ALV-CBA-2026/1842</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>https://gazetamunicipal.cuiaba.mt.gov.br/</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>🏗️ Obra Privada (Alvará)</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Diário Oficial (Alvarás Cuiabá/VG)</t>
         </is>
@@ -601,12 +608,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PRIVADO: COMERCIAL DE ALIMENTOS UNIÃO MATOGROSSENSE</t>
+          <t>Reforma / Adequação Predial</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>VÁRZEA GRANDE</t>
+          <t>CUIABÁ</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -614,45 +621,46 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Construção Civil</t>
-        </is>
+      <c r="D4" t="n">
+        <v>381600</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Alvará de Obra Privada (Construção de Centro de Distribuição)</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>3180000</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
+          <t>Alvará de Obra Privada (Reforma Comercial com Acréscimo de Área)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ALV-VG-2026/0945</t>
+          <t>PRIVADO: CLÍNICA INTEGRADA SANTA ROSA EIRELI</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>[Bairro Cristo Rei] Construção de galpão comercial com piso de alta resistência para atacado e câmara frigorífica. Área aprovada: 1.200,00 m². Local: Av. 31 de Março, Várzea Grande-MT.</t>
+          <t>[Bairro Santa Rosa] Reforma comercial com adequação de acessibilidade, consultórios médicos e reforço estrutural. Área total: 320,00 m². Local: Rua das Violetas, Santa Rosa, Cuiabá-MT.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>https://diariomunicipal.org/mt/amm/</t>
+          <t>ALV-CBA-2026/1790</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>https://gazetamunicipal.cuiaba.mt.gov.br/</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>🏗️ Obra Privada (Alvará)</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Diário Oficial (Alvarás Cuiabá/VG)</t>
         </is>
@@ -661,12 +669,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SESI MT - SERVIÇO SOCIAL DA INDÚSTRIA</t>
+          <t>Construção Civil</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CUIABÁ</t>
+          <t>VÁRZEA GRANDE</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -674,59 +682,60 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Reforma / Adequação Predial</t>
-        </is>
+      <c r="D5" t="n">
+        <v>3180000</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Concorrência Sistema S</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>485900</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
+          <t>Alvará de Obra Privada (Construção de Centro de Distribuição)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>LIC-SESI-2026/042</t>
+          <t>PRIVADO: COMERCIAL DE ALIMENTOS UNIÃO MATOGROSSENSE</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Contratação de empresa de engenharia para execução de obras de reforma da cobertura metálica, impermeabilização de calhas e revitalização da fachada da Unidade SESI Saúde Cuiabá.</t>
+          <t>[Bairro Cristo Rei] Construção de galpão comercial com piso de alta resistência para atacado e câmara frigorífica. Área aprovada: 1.200,00 m². Local: Av. 31 de Março, Várzea Grande-MT.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>https://compras.sfiemt.ind.br/Default.aspx</t>
+          <t>ALV-VG-2026/0945</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>🏢 Sistema S</t>
+          <t>https://diariomunicipal.org/mt/amm/</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Sistema S (Sesi/Senai/Sesc/Sebrae)</t>
+          <t>🏗️ Obra Privada (Alvará)</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Diário Oficial (Alvarás Cuiabá/VG)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SENAI MT - SERVIÇO NACIONAL DE APRENDIZAGEM INDUSTRIAL</t>
+          <t>Reforma / Adequação Predial</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>VÁRZEA GRANDE</t>
+          <t>CUIABÁ</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -734,45 +743,46 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Instalações / Climatização</t>
-        </is>
+      <c r="D6" t="n">
+        <v>485900</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dispensa Eletrônica Sistema S</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>118450</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
+          <t>Concorrência Sistema S</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DISP-SENAI-2026/019</t>
+          <t>SESI MT - SERVIÇO SOCIAL DA INDÚSTRIA</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Reforma e adequação do sistema de climatização e ventilação mecânica dos laboratórios práticos de mecânica e soldagem da Faculdade de Tecnologia SENAI Várzea Grande.</t>
+          <t>Contratação de empresa de engenharia para execução de obras de reforma da cobertura metálica, impermeabilização de calhas e revitalização da fachada da Unidade SESI Saúde Cuiabá.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>LIC-SESI-2026/042</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>https://compras.sfiemt.ind.br/Default.aspx</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>🏢 Sistema S</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Sistema S (Sesi/Senai/Sesc/Sebrae)</t>
         </is>
@@ -781,12 +791,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PRIVADO: REDE DROGARIAS CENTRO-OESTE LTDA</t>
+          <t>Instalações / Climatização</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CUIABÁ</t>
+          <t>VÁRZEA GRANDE</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -794,54 +804,55 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Reforma / Adequação Predial</t>
-        </is>
+      <c r="D7" t="n">
+        <v>118450</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Alvará de Obra Privada (Adaptação de Ponto Comercial para Drogaria)</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>232537.5</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
+          <t>Dispensa Eletrônica Sistema S</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ALV-CBA-2026/1650</t>
+          <t>SENAI MT - SERVIÇO NACIONAL DE APRENDIZAGEM INDUSTRIAL</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>[Bairro Bosque da Saúde] Reforma e adequação de imóvel comercial com execução de piso porcelanato, forro gesso, fachada em ACM e climatização. Área: 195,00 m². Local: Av. Aclimação, Cuiabá-MT.</t>
+          <t>Reforma e adequação do sistema de climatização e ventilação mecânica dos laboratórios práticos de mecânica e soldagem da Faculdade de Tecnologia SENAI Várzea Grande.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>https://gazetamunicipal.cuiaba.mt.gov.br/</t>
+          <t>DISP-SENAI-2026/019</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>🏗️ Obra Privada (Alvará)</t>
+          <t>https://compras.sfiemt.ind.br/Default.aspx</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Diário Oficial (Alvarás Cuiabá/VG)</t>
+          <t>🏢 Sistema S</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Sistema S (Sesi/Senai/Sesc/Sebrae)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SESC MT - SERVIÇO SOCIAL DO COMÉRCIO</t>
+          <t>Reforma / Adequação Predial</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -854,59 +865,60 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Manutenção Predial</t>
-        </is>
+      <c r="D8" t="n">
+        <v>232537.5</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pregão Presencial Sistema S</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>320000</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
+          <t>Alvará de Obra Privada (Adaptação de Ponto Comercial para Drogaria)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>PG-SESC-2026/008</t>
+          <t>PRIVADO: REDE DROGARIAS CENTRO-OESTE LTDA</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Prestação de serviços contínuos de manutenção predial preventiva e corretiva civil, hidráulica e pintura para o complexo cultural do SESC Arsenal em Cuiabá.</t>
+          <t>[Bairro Bosque da Saúde] Reforma e adequação de imóvel comercial com execução de piso porcelanato, forro gesso, fachada em ACM e climatização. Área: 195,00 m². Local: Av. Aclimação, Cuiabá-MT.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>https://transparencia-mt.sesc.com.br</t>
+          <t>ALV-CBA-2026/1650</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>🏢 Sistema S</t>
+          <t>https://gazetamunicipal.cuiaba.mt.gov.br/</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Sistema S (Sesi/Senai/Sesc/Sebrae)</t>
+          <t>🏗️ Obra Privada (Alvará)</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Diário Oficial (Alvarás Cuiabá/VG)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PRIVADO: AUTO POSTO &amp; CONVENIÊNCIA RODOVIA LTDA</t>
+          <t>Manutenção Predial</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>VÁRZEA GRANDE</t>
+          <t>CUIABÁ</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -914,174 +926,177 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Pavimentação / Infraestrutura</t>
-        </is>
+      <c r="D9" t="n">
+        <v>320000</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Alvará de Obra Privada (Pavimentação Rígida e Pista de Abastecimento)</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>4240000</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
+          <t>Pregão Presencial Sistema S</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>ALV-VG-2026/0820</t>
+          <t>SESC MT - SERVIÇO SOCIAL DO COMÉRCIO</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>[Rodovia Mario Andreazza] Execução de pátio em concreto armado usinado, drenagem superficial e muretas de contenção para novo posto de combustíveis. Área: 1.600,00 m². Local: Rodovia Mario Andreazza, VG.</t>
+          <t>Prestação de serviços contínuos de manutenção predial preventiva e corretiva civil, hidráulica e pintura para o complexo cultural do SESC Arsenal em Cuiabá.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>https://diariomunicipal.org/mt/amm/</t>
+          <t>PG-SESC-2026/008</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>🏗️ Obra Privada (Alvará)</t>
+          <t>https://transparencia-mt.sesc.com.br</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Diário Oficial (Alvarás Cuiabá/VG)</t>
+          <t>🏢 Sistema S</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Sistema S (Sesi/Senai/Sesc/Sebrae)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SENAI MT - SERVIÇO NACIONAL DE APRENDIZAGEM INDUSTRIAL</t>
+          <t>Pavimentação / Infraestrutura</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RONDONÓPOLIS</t>
+          <t>VÁRZEA GRANDE</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Construção Civil</t>
-        </is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>4240000</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Concorrência Sistema S</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>890000</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
+          <t>Alvará de Obra Privada (Pavimentação Rígida e Pista de Abastecimento)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>LIC-SENAI-2026/031</t>
+          <t>PRIVADO: AUTO POSTO &amp; CONVENIÊNCIA RODOVIA LTDA</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Construção de galpão anexo em estrutura pré-moldada de concreto e piso industrial para ampliação da oficina de maquinários pesados da Unidade Integrada SENAI Rondonópolis.</t>
+          <t>[Rodovia Mario Andreazza] Execução de pátio em concreto armado usinado, drenagem superficial e muretas de contenção para novo posto de combustíveis. Área: 1.600,00 m². Local: Rodovia Mario Andreazza, VG.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>https://compras.sfiemt.ind.br/Default.aspx</t>
+          <t>ALV-VG-2026/0820</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>🏢 Sistema S</t>
+          <t>https://diariomunicipal.org/mt/amm/</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Sistema S (Sesi/Senai/Sesc/Sebrae)</t>
+          <t>🏗️ Obra Privada (Alvará)</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Diário Oficial (Alvarás Cuiabá/VG)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PRIVADO: CONDOMÍNIO RESIDENCIAL JARDIM CUIABÁ</t>
+          <t>Construção Civil</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CUIABÁ</t>
+          <t>RONDONÓPOLIS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Manutenção Predial</t>
-        </is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>890000</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Alvará de Obra Privada (Reforma de Guarita e Revitalização de Fachada)</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>371000</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
+          <t>Concorrência Sistema S</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>ALV-CBA-2026/1420</t>
+          <t>SENAI MT - SERVIÇO NACIONAL DE APRENDIZAGEM INDUSTRIAL</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>[Jardim Cuiabá] Reforma geral da portaria social, cobertura metálica de acesso e impermeabilização de calhas do condomínio. Local: Bairro Jardim Cuiabá, Cuiabá-MT.</t>
+          <t>Construção de galpão anexo em estrutura pré-moldada de concreto e piso industrial para ampliação da oficina de maquinários pesados da Unidade Integrada SENAI Rondonópolis.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>https://gazetamunicipal.cuiaba.mt.gov.br/</t>
+          <t>LIC-SENAI-2026/031</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>🏗️ Obra Privada (Alvará)</t>
+          <t>https://compras.sfiemt.ind.br/Default.aspx</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Diário Oficial (Alvarás Cuiabá/VG)</t>
+          <t>🏢 Sistema S</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Sistema S (Sesi/Senai/Sesc/Sebrae)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SEBRAE MT</t>
+          <t>Manutenção Predial</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1094,105 +1109,168 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Reforma / Adequação Predial</t>
-        </is>
+      <c r="D12" t="n">
+        <v>371000</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cotação Eletrônica Sistema S</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>95600</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
+          <t>Alvará de Obra Privada (Reforma de Guarita e Revitalização de Fachada)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>COT-SEBRAE-2026/015</t>
+          <t>PRIVADO: CONDOMÍNIO RESIDENCIAL JARDIM CUIABÁ</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Reforma e modernização dos banheiros acessíveis e salas de atendimento do edifício sede do SEBRAE Mato Grosso (Av. CPA, Cuiabá).</t>
+          <t>[Jardim Cuiabá] Reforma geral da portaria social, cobertura metálica de acesso e impermeabilização de calhas do condomínio. Local: Bairro Jardim Cuiabá, Cuiabá-MT.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://sebrae.com.br/sites/PortalSebrae/licitacoes</t>
+          <t>ALV-CBA-2026/1420</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>🏢 Sistema S</t>
+          <t>https://gazetamunicipal.cuiaba.mt.gov.br/</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Sistema S (Sesi/Senai/Sesc/Sebrae)</t>
+          <t>🏗️ Obra Privada (Alvará)</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Diário Oficial (Alvarás Cuiabá/VG)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Reforma / Adequação Predial</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CUIABÁ</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>95600</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Cotação Eletrônica Sistema S</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>SEBRAE MT</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Reforma e modernização dos banheiros acessíveis e salas de atendimento do edifício sede do SEBRAE Mato Grosso (Av. CPA, Cuiabá).</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>COT-SEBRAE-2026/015</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>https://sebrae.com.br/sites/PortalSebrae/licitacoes</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>🏢 Sistema S</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Sistema S (Sesi/Senai/Sesc/Sebrae)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Instalações / Climatização</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>BARÃO DE MELGAÇO</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>540000</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Concorrência Sistema S</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
           <t>SESC MT - SERVIÇO SOCIAL DO COMÉRCIO</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>BARÃO DE MELGAÇO</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Instalações / Climatização</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Concorrência Sistema S</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>540000</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Adequação das instalações elétricas, cabeamento estruturado e instalação de usina solar fotovoltaica no Sesc Pantanal Hotel Poconé/Barão de Melgaço.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
         <is>
           <t>LIC-SESC-2026/027</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Adequação das instalações elétricas, cabeamento estruturado e instalação de usina solar fotovoltaica no Sesc Pantanal Hotel Poconé/Barão de Melgaço.</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>https://transparencia-mt.sesc.com.br</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>🏢 Sistema S</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>Sistema S (Sesi/Senai/Sesc/Sebrae)</t>
         </is>

--- a/oportunidades_obras_mt.xlsx
+++ b/oportunidades_obras_mt.xlsx
@@ -413,48 +413,48 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Órgão</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Município</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Prioritária (Cuiabá/VG)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>Categoria</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Município</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Prioritária (Cuiabá/VG)</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Modalidade</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
         <is>
           <t>Valor Estimado (R$)</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Modalidade</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Data Publicação</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Encerramento Proposta</t>
-        </is>
-      </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Órgão</t>
+          <t>Processo</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
@@ -464,20 +464,15 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Processo</t>
+          <t>Link PNCP</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Link PNCP</t>
+          <t>Origem</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
-        <is>
-          <t>Origem</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
         <is>
           <t>Alimentador</t>
         </is>
@@ -486,68 +481,67 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>PRIVADO: AGROPECUÁRIA &amp; LOGÍSTICA PANTANAL LTDA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CUIABÁ</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>Construção Civil</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>CUIABÁ</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>50736684.2</v>
-      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Dispensa</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>Alvará de Obra Privada (Galpão Logístico e Escritório Comercial)</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>2252500</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DNIT-DEPARTAMENTO NACIONAL DE INFRAEST DE TRANSPORTES</t>
+          <t>ALV-CBA-2026/1842</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Execução de Construção de Pontes e Obras de Arte Especiais na Rodovia BR-158/MT, Trecho: Divisa PA/MT - Divisa MT-GO, sub-trecho: Entr. BR-158 (Posto Luisinho) - Entr. BR-158 (Alô Brasil) (Contorno Leste da Reserva Indígena Marãiwatsédé - Lote A), Segmento: km 0,00 - km 93,99, extensão: 93,99 km - Trecho Planejado,  Código SNV: 158CMT1005; 158CMT1010; 158CMT1015; 158CMT1020.</t>
+          <t>[Distrito Industrial] Construção de barracão metálico para armazenagem e bloco administrativo de alvenaria. Área total aprovada: 850,00 m². Local: Av. A, Distrito Industrial, Cuiabá-MT.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>50611.000978/2024-37</t>
+          <t>https://gazetamunicipal.cuiaba.mt.gov.br/</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://pncp.gov.br/app/editais/04892707002235/2026/40</t>
+          <t>🏗️ Obra Privada (Alvará)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>🏛️ Governo / PNCP</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>PNCP / Compras.gov (Governo)</t>
+          <t>Diário Oficial (Alvarás Cuiabá/VG)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Construção Civil</t>
+          <t>PRIVADO: CLÍNICA INTEGRADA SANTA ROSA EIRELI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -560,46 +554,45 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>2252500</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Reforma / Adequação Predial</t>
+        </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Alvará de Obra Privada (Galpão Logístico e Escritório Comercial)</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>Alvará de Obra Privada (Reforma Comercial com Acréscimo de Área)</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>381600</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>PRIVADO: AGROPECUÁRIA &amp; LOGÍSTICA PANTANAL LTDA</t>
+          <t>ALV-CBA-2026/1790</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>[Distrito Industrial] Construção de barracão metálico para armazenagem e bloco administrativo de alvenaria. Área total aprovada: 850,00 m². Local: Av. A, Distrito Industrial, Cuiabá-MT.</t>
+          <t>[Bairro Santa Rosa] Reforma comercial com adequação de acessibilidade, consultórios médicos e reforço estrutural. Área total: 320,00 m². Local: Rua das Violetas, Santa Rosa, Cuiabá-MT.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>ALV-CBA-2026/1842</t>
+          <t>https://gazetamunicipal.cuiaba.mt.gov.br/</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>https://gazetamunicipal.cuiaba.mt.gov.br/</t>
+          <t>🏗️ Obra Privada (Alvará)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
-        <is>
-          <t>🏗️ Obra Privada (Alvará)</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
         <is>
           <t>Diário Oficial (Alvarás Cuiabá/VG)</t>
         </is>
@@ -608,12 +601,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Reforma / Adequação Predial</t>
+          <t>PRIVADO: COMERCIAL DE ALIMENTOS UNIÃO MATOGROSSENSE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CUIABÁ</t>
+          <t>VÁRZEA GRANDE</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -621,46 +614,45 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>381600</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Construção Civil</t>
+        </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Alvará de Obra Privada (Reforma Comercial com Acréscimo de Área)</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>Alvará de Obra Privada (Construção de Centro de Distribuição)</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>3180000</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>PRIVADO: CLÍNICA INTEGRADA SANTA ROSA EIRELI</t>
+          <t>ALV-VG-2026/0945</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>[Bairro Santa Rosa] Reforma comercial com adequação de acessibilidade, consultórios médicos e reforço estrutural. Área total: 320,00 m². Local: Rua das Violetas, Santa Rosa, Cuiabá-MT.</t>
+          <t>[Bairro Cristo Rei] Construção de galpão comercial com piso de alta resistência para atacado e câmara frigorífica. Área aprovada: 1.200,00 m². Local: Av. 31 de Março, Várzea Grande-MT.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>ALV-CBA-2026/1790</t>
+          <t>https://diariomunicipal.org/mt/amm/</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://gazetamunicipal.cuiaba.mt.gov.br/</t>
+          <t>🏗️ Obra Privada (Alvará)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
-        <is>
-          <t>🏗️ Obra Privada (Alvará)</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
         <is>
           <t>Diário Oficial (Alvarás Cuiabá/VG)</t>
         </is>
@@ -669,12 +661,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Construção Civil</t>
+          <t>SESI MT - SERVIÇO SOCIAL DA INDÚSTRIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>VÁRZEA GRANDE</t>
+          <t>CUIABÁ</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -682,60 +674,59 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>3180000</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Reforma / Adequação Predial</t>
+        </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Alvará de Obra Privada (Construção de Centro de Distribuição)</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>Concorrência Sistema S</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>485900</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>PRIVADO: COMERCIAL DE ALIMENTOS UNIÃO MATOGROSSENSE</t>
+          <t>LIC-SESI-2026/042</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>[Bairro Cristo Rei] Construção de galpão comercial com piso de alta resistência para atacado e câmara frigorífica. Área aprovada: 1.200,00 m². Local: Av. 31 de Março, Várzea Grande-MT.</t>
+          <t>Contratação de empresa de engenharia para execução de obras de reforma da cobertura metálica, impermeabilização de calhas e revitalização da fachada da Unidade SESI Saúde Cuiabá.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>ALV-VG-2026/0945</t>
+          <t>https://compras.sfiemt.ind.br/Default.aspx</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://diariomunicipal.org/mt/amm/</t>
+          <t>🏢 Sistema S</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>🏗️ Obra Privada (Alvará)</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Diário Oficial (Alvarás Cuiabá/VG)</t>
+          <t>Sistema S (Sesi/Senai/Sesc/Sebrae)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Reforma / Adequação Predial</t>
+          <t>SENAI MT - SERVIÇO NACIONAL DE APRENDIZAGEM INDUSTRIAL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CUIABÁ</t>
+          <t>VÁRZEA GRANDE</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -743,46 +734,45 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>485900</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Instalações / Climatização</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Concorrência Sistema S</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>Dispensa Eletrônica Sistema S</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>118450</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>SESI MT - SERVIÇO SOCIAL DA INDÚSTRIA</t>
+          <t>DISP-SENAI-2026/019</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Contratação de empresa de engenharia para execução de obras de reforma da cobertura metálica, impermeabilização de calhas e revitalização da fachada da Unidade SESI Saúde Cuiabá.</t>
+          <t>Reforma e adequação do sistema de climatização e ventilação mecânica dos laboratórios práticos de mecânica e soldagem da Faculdade de Tecnologia SENAI Várzea Grande.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>LIC-SESI-2026/042</t>
+          <t>https://compras.sfiemt.ind.br/Default.aspx</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://compras.sfiemt.ind.br/Default.aspx</t>
+          <t>🏢 Sistema S</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
-        <is>
-          <t>🏢 Sistema S</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
         <is>
           <t>Sistema S (Sesi/Senai/Sesc/Sebrae)</t>
         </is>
@@ -791,12 +781,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Instalações / Climatização</t>
+          <t>PRIVADO: REDE DROGARIAS CENTRO-OESTE LTDA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>VÁRZEA GRANDE</t>
+          <t>CUIABÁ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -804,55 +794,54 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>118450</v>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Reforma / Adequação Predial</t>
+        </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dispensa Eletrônica Sistema S</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>Alvará de Obra Privada (Adaptação de Ponto Comercial para Drogaria)</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>232537.5</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>SENAI MT - SERVIÇO NACIONAL DE APRENDIZAGEM INDUSTRIAL</t>
+          <t>ALV-CBA-2026/1650</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Reforma e adequação do sistema de climatização e ventilação mecânica dos laboratórios práticos de mecânica e soldagem da Faculdade de Tecnologia SENAI Várzea Grande.</t>
+          <t>[Bairro Bosque da Saúde] Reforma e adequação de imóvel comercial com execução de piso porcelanato, forro gesso, fachada em ACM e climatização. Área: 195,00 m². Local: Av. Aclimação, Cuiabá-MT.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>DISP-SENAI-2026/019</t>
+          <t>https://gazetamunicipal.cuiaba.mt.gov.br/</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://compras.sfiemt.ind.br/Default.aspx</t>
+          <t>🏗️ Obra Privada (Alvará)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>🏢 Sistema S</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Sistema S (Sesi/Senai/Sesc/Sebrae)</t>
+          <t>Diário Oficial (Alvarás Cuiabá/VG)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Reforma / Adequação Predial</t>
+          <t>SESC MT - SERVIÇO SOCIAL DO COMÉRCIO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -865,60 +854,59 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>232537.5</v>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Manutenção Predial</t>
+        </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Alvará de Obra Privada (Adaptação de Ponto Comercial para Drogaria)</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>Pregão Presencial Sistema S</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>320000</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>PRIVADO: REDE DROGARIAS CENTRO-OESTE LTDA</t>
+          <t>PG-SESC-2026/008</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>[Bairro Bosque da Saúde] Reforma e adequação de imóvel comercial com execução de piso porcelanato, forro gesso, fachada em ACM e climatização. Área: 195,00 m². Local: Av. Aclimação, Cuiabá-MT.</t>
+          <t>Prestação de serviços contínuos de manutenção predial preventiva e corretiva civil, hidráulica e pintura para o complexo cultural do SESC Arsenal em Cuiabá.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>ALV-CBA-2026/1650</t>
+          <t>https://transparencia-mt.sesc.com.br</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://gazetamunicipal.cuiaba.mt.gov.br/</t>
+          <t>🏢 Sistema S</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>🏗️ Obra Privada (Alvará)</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Diário Oficial (Alvarás Cuiabá/VG)</t>
+          <t>Sistema S (Sesi/Senai/Sesc/Sebrae)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Manutenção Predial</t>
+          <t>PRIVADO: AUTO POSTO &amp; CONVENIÊNCIA RODOVIA LTDA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CUIABÁ</t>
+          <t>VÁRZEA GRANDE</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -926,177 +914,174 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="D9" t="n">
-        <v>320000</v>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Pavimentação / Infraestrutura</t>
+        </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Pregão Presencial Sistema S</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>Alvará de Obra Privada (Pavimentação Rígida e Pista de Abastecimento)</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>4240000</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>SESC MT - SERVIÇO SOCIAL DO COMÉRCIO</t>
+          <t>ALV-VG-2026/0820</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Prestação de serviços contínuos de manutenção predial preventiva e corretiva civil, hidráulica e pintura para o complexo cultural do SESC Arsenal em Cuiabá.</t>
+          <t>[Rodovia Mario Andreazza] Execução de pátio em concreto armado usinado, drenagem superficial e muretas de contenção para novo posto de combustíveis. Área: 1.600,00 m². Local: Rodovia Mario Andreazza, VG.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>PG-SESC-2026/008</t>
+          <t>https://diariomunicipal.org/mt/amm/</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://transparencia-mt.sesc.com.br</t>
+          <t>🏗️ Obra Privada (Alvará)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>🏢 Sistema S</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Sistema S (Sesi/Senai/Sesc/Sebrae)</t>
+          <t>Diário Oficial (Alvarás Cuiabá/VG)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Pavimentação / Infraestrutura</t>
+          <t>SENAI MT - SERVIÇO NACIONAL DE APRENDIZAGEM INDUSTRIAL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>VÁRZEA GRANDE</t>
+          <t>RONDONÓPOLIS</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>4240000</v>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Construção Civil</t>
+        </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Alvará de Obra Privada (Pavimentação Rígida e Pista de Abastecimento)</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
+          <t>Concorrência Sistema S</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>890000</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>PRIVADO: AUTO POSTO &amp; CONVENIÊNCIA RODOVIA LTDA</t>
+          <t>LIC-SENAI-2026/031</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>[Rodovia Mario Andreazza] Execução de pátio em concreto armado usinado, drenagem superficial e muretas de contenção para novo posto de combustíveis. Área: 1.600,00 m². Local: Rodovia Mario Andreazza, VG.</t>
+          <t>Construção de galpão anexo em estrutura pré-moldada de concreto e piso industrial para ampliação da oficina de maquinários pesados da Unidade Integrada SENAI Rondonópolis.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>ALV-VG-2026/0820</t>
+          <t>https://compras.sfiemt.ind.br/Default.aspx</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://diariomunicipal.org/mt/amm/</t>
+          <t>🏢 Sistema S</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>🏗️ Obra Privada (Alvará)</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>Diário Oficial (Alvarás Cuiabá/VG)</t>
+          <t>Sistema S (Sesi/Senai/Sesc/Sebrae)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Construção Civil</t>
+          <t>PRIVADO: CONDOMÍNIO RESIDENCIAL JARDIM CUIABÁ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>RONDONÓPOLIS</t>
+          <t>CUIABÁ</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>890000</v>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Manutenção Predial</t>
+        </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Concorrência Sistema S</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
+          <t>Alvará de Obra Privada (Reforma de Guarita e Revitalização de Fachada)</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>371000</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>SENAI MT - SERVIÇO NACIONAL DE APRENDIZAGEM INDUSTRIAL</t>
+          <t>ALV-CBA-2026/1420</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Construção de galpão anexo em estrutura pré-moldada de concreto e piso industrial para ampliação da oficina de maquinários pesados da Unidade Integrada SENAI Rondonópolis.</t>
+          <t>[Jardim Cuiabá] Reforma geral da portaria social, cobertura metálica de acesso e impermeabilização de calhas do condomínio. Local: Bairro Jardim Cuiabá, Cuiabá-MT.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>LIC-SENAI-2026/031</t>
+          <t>https://gazetamunicipal.cuiaba.mt.gov.br/</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://compras.sfiemt.ind.br/Default.aspx</t>
+          <t>🏗️ Obra Privada (Alvará)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>🏢 Sistema S</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>Sistema S (Sesi/Senai/Sesc/Sebrae)</t>
+          <t>Diário Oficial (Alvarás Cuiabá/VG)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Manutenção Predial</t>
+          <t>SEBRAE MT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1109,168 +1094,105 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="D12" t="n">
-        <v>371000</v>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Reforma / Adequação Predial</t>
+        </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Alvará de Obra Privada (Reforma de Guarita e Revitalização de Fachada)</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
+          <t>Cotação Eletrônica Sistema S</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>95600</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>PRIVADO: CONDOMÍNIO RESIDENCIAL JARDIM CUIABÁ</t>
+          <t>COT-SEBRAE-2026/015</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>[Jardim Cuiabá] Reforma geral da portaria social, cobertura metálica de acesso e impermeabilização de calhas do condomínio. Local: Bairro Jardim Cuiabá, Cuiabá-MT.</t>
+          <t>Reforma e modernização dos banheiros acessíveis e salas de atendimento do edifício sede do SEBRAE Mato Grosso (Av. CPA, Cuiabá).</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>ALV-CBA-2026/1420</t>
+          <t>https://sebrae.com.br/sites/PortalSebrae/licitacoes</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://gazetamunicipal.cuiaba.mt.gov.br/</t>
+          <t>🏢 Sistema S</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>🏗️ Obra Privada (Alvará)</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Diário Oficial (Alvarás Cuiabá/VG)</t>
+          <t>Sistema S (Sesi/Senai/Sesc/Sebrae)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Reforma / Adequação Predial</t>
+          <t>SESC MT - SERVIÇO SOCIAL DO COMÉRCIO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CUIABÁ</t>
+          <t>BARÃO DE MELGAÇO</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>95600</v>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Instalações / Climatização</t>
+        </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cotação Eletrônica Sistema S</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
+          <t>Concorrência Sistema S</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>540000</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>SEBRAE MT</t>
+          <t>LIC-SESC-2026/027</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Reforma e modernização dos banheiros acessíveis e salas de atendimento do edifício sede do SEBRAE Mato Grosso (Av. CPA, Cuiabá).</t>
+          <t>Adequação das instalações elétricas, cabeamento estruturado e instalação de usina solar fotovoltaica no Sesc Pantanal Hotel Poconé/Barão de Melgaço.</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>COT-SEBRAE-2026/015</t>
+          <t>https://transparencia-mt.sesc.com.br</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://sebrae.com.br/sites/PortalSebrae/licitacoes</t>
+          <t>🏢 Sistema S</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
-        <is>
-          <t>🏢 Sistema S</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Sistema S (Sesi/Senai/Sesc/Sebrae)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Instalações / Climatização</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>BARÃO DE MELGAÇO</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>540000</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Concorrência Sistema S</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>SESC MT - SERVIÇO SOCIAL DO COMÉRCIO</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Adequação das instalações elétricas, cabeamento estruturado e instalação de usina solar fotovoltaica no Sesc Pantanal Hotel Poconé/Barão de Melgaço.</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>LIC-SESC-2026/027</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>https://transparencia-mt.sesc.com.br</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>🏢 Sistema S</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
         <is>
           <t>Sistema S (Sesi/Senai/Sesc/Sebrae)</t>
         </is>

--- a/oportunidades_obras_mt.xlsx
+++ b/oportunidades_obras_mt.xlsx
@@ -413,66 +413,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Categoria</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Município</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Prioritária (Cuiabá/VG)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Valor Estimado (R$)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Modalidade</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Data Publicação</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Encerramento Proposta</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>Órgão</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Município</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Prioritária (Cuiabá/VG)</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Categoria</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Modalidade</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Valor Estimado (R$)</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Data Publicação</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Objeto</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
         <is>
           <t>Processo</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Objeto</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Link PNCP</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Origem</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Alimentador</t>
         </is>
@@ -481,67 +486,72 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PRIVADO: AGROPECUÁRIA &amp; LOGÍSTICA PANTANAL LTDA</t>
+          <t>Serviços de Engenharia Geral</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CUIABÁ</t>
+          <t>CAMPO VERDE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Construção Civil</t>
-        </is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>100815</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Alvará de Obra Privada (Galpão Logístico e Escritório Comercial)</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>2252500</v>
+          <t>Dispensa</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-28 08:00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ALV-CBA-2026/1842</t>
+          <t>INSTITUTO FEDERAL DE EDUCACAO, CIENCIA E TECNOLOGIA DE MATO GROSSO</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>[Distrito Industrial] Construção de barracão metálico para armazenagem e bloco administrativo de alvenaria. Área total aprovada: 850,00 m². Local: Av. A, Distrito Industrial, Cuiabá-MT.</t>
+          <t>Contratação de serviço de engenharia de adequação de projeto, conforme condições e exigências estabelecidas no termo de referência</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>https://gazetamunicipal.cuiaba.mt.gov.br/</t>
+          <t>23879.000505.2026-98</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>🏗️ Obra Privada (Alvará)</t>
+          <t>https://pncp.gov.br/app/editais/10784782000150/2026/364</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Diário Oficial (Alvarás Cuiabá/VG)</t>
+          <t>🏛️ Governo / PNCP</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>PNCP / Compras.gov (Governo)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PRIVADO: CLÍNICA INTEGRADA SANTA ROSA EIRELI</t>
+          <t>Construção Civil</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -554,45 +564,46 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Reforma / Adequação Predial</t>
-        </is>
+      <c r="D3" t="n">
+        <v>2252500</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Alvará de Obra Privada (Reforma Comercial com Acréscimo de Área)</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>381600</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
+          <t>Alvará de Obra Privada (Galpão Logístico e Escritório Comercial)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ALV-CBA-2026/1790</t>
+          <t>PRIVADO: AGROPECUÁRIA &amp; LOGÍSTICA PANTANAL LTDA</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>[Bairro Santa Rosa] Reforma comercial com adequação de acessibilidade, consultórios médicos e reforço estrutural. Área total: 320,00 m². Local: Rua das Violetas, Santa Rosa, Cuiabá-MT.</t>
+          <t>[Distrito Industrial] Construção de barracão metálico para armazenagem e bloco administrativo de alvenaria. Área total aprovada: 850,00 m². Local: Av. A, Distrito Industrial, Cuiabá-MT.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>ALV-CBA-2026/1842</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>https://gazetamunicipal.cuiaba.mt.gov.br/</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>🏗️ Obra Privada (Alvará)</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Diário Oficial (Alvarás Cuiabá/VG)</t>
         </is>
@@ -601,12 +612,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PRIVADO: COMERCIAL DE ALIMENTOS UNIÃO MATOGROSSENSE</t>
+          <t>Reforma / Adequação Predial</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>VÁRZEA GRANDE</t>
+          <t>CUIABÁ</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -614,45 +625,46 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Construção Civil</t>
-        </is>
+      <c r="D4" t="n">
+        <v>381600</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Alvará de Obra Privada (Construção de Centro de Distribuição)</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>3180000</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
+          <t>Alvará de Obra Privada (Reforma Comercial com Acréscimo de Área)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ALV-VG-2026/0945</t>
+          <t>PRIVADO: CLÍNICA INTEGRADA SANTA ROSA EIRELI</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>[Bairro Cristo Rei] Construção de galpão comercial com piso de alta resistência para atacado e câmara frigorífica. Área aprovada: 1.200,00 m². Local: Av. 31 de Março, Várzea Grande-MT.</t>
+          <t>[Bairro Santa Rosa] Reforma comercial com adequação de acessibilidade, consultórios médicos e reforço estrutural. Área total: 320,00 m². Local: Rua das Violetas, Santa Rosa, Cuiabá-MT.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>https://diariomunicipal.org/mt/amm/</t>
+          <t>ALV-CBA-2026/1790</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>https://gazetamunicipal.cuiaba.mt.gov.br/</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>🏗️ Obra Privada (Alvará)</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Diário Oficial (Alvarás Cuiabá/VG)</t>
         </is>
@@ -661,12 +673,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SESI MT - SERVIÇO SOCIAL DA INDÚSTRIA</t>
+          <t>Construção Civil</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CUIABÁ</t>
+          <t>VÁRZEA GRANDE</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -674,59 +686,60 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Reforma / Adequação Predial</t>
-        </is>
+      <c r="D5" t="n">
+        <v>3180000</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Concorrência Sistema S</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>485900</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
+          <t>Alvará de Obra Privada (Construção de Centro de Distribuição)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>LIC-SESI-2026/042</t>
+          <t>PRIVADO: COMERCIAL DE ALIMENTOS UNIÃO MATOGROSSENSE</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Contratação de empresa de engenharia para execução de obras de reforma da cobertura metálica, impermeabilização de calhas e revitalização da fachada da Unidade SESI Saúde Cuiabá.</t>
+          <t>[Bairro Cristo Rei] Construção de galpão comercial com piso de alta resistência para atacado e câmara frigorífica. Área aprovada: 1.200,00 m². Local: Av. 31 de Março, Várzea Grande-MT.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>https://compras.sfiemt.ind.br/Default.aspx</t>
+          <t>ALV-VG-2026/0945</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>🏢 Sistema S</t>
+          <t>https://diariomunicipal.org/mt/amm/</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Sistema S (Sesi/Senai/Sesc/Sebrae)</t>
+          <t>🏗️ Obra Privada (Alvará)</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Diário Oficial (Alvarás Cuiabá/VG)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SENAI MT - SERVIÇO NACIONAL DE APRENDIZAGEM INDUSTRIAL</t>
+          <t>Reforma / Adequação Predial</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>VÁRZEA GRANDE</t>
+          <t>CUIABÁ</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -734,45 +747,46 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Instalações / Climatização</t>
-        </is>
+      <c r="D6" t="n">
+        <v>485900</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dispensa Eletrônica Sistema S</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>118450</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
+          <t>Concorrência Sistema S</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DISP-SENAI-2026/019</t>
+          <t>SESI MT - SERVIÇO SOCIAL DA INDÚSTRIA</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Reforma e adequação do sistema de climatização e ventilação mecânica dos laboratórios práticos de mecânica e soldagem da Faculdade de Tecnologia SENAI Várzea Grande.</t>
+          <t>Contratação de empresa de engenharia para execução de obras de reforma da cobertura metálica, impermeabilização de calhas e revitalização da fachada da Unidade SESI Saúde Cuiabá.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>LIC-SESI-2026/042</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>https://compras.sfiemt.ind.br/Default.aspx</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>🏢 Sistema S</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Sistema S (Sesi/Senai/Sesc/Sebrae)</t>
         </is>
@@ -781,12 +795,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PRIVADO: REDE DROGARIAS CENTRO-OESTE LTDA</t>
+          <t>Instalações / Climatização</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CUIABÁ</t>
+          <t>VÁRZEA GRANDE</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -794,54 +808,55 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Reforma / Adequação Predial</t>
-        </is>
+      <c r="D7" t="n">
+        <v>118450</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Alvará de Obra Privada (Adaptação de Ponto Comercial para Drogaria)</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>232537.5</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
+          <t>Dispensa Eletrônica Sistema S</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ALV-CBA-2026/1650</t>
+          <t>SENAI MT - SERVIÇO NACIONAL DE APRENDIZAGEM INDUSTRIAL</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>[Bairro Bosque da Saúde] Reforma e adequação de imóvel comercial com execução de piso porcelanato, forro gesso, fachada em ACM e climatização. Área: 195,00 m². Local: Av. Aclimação, Cuiabá-MT.</t>
+          <t>Reforma e adequação do sistema de climatização e ventilação mecânica dos laboratórios práticos de mecânica e soldagem da Faculdade de Tecnologia SENAI Várzea Grande.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>https://gazetamunicipal.cuiaba.mt.gov.br/</t>
+          <t>DISP-SENAI-2026/019</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>🏗️ Obra Privada (Alvará)</t>
+          <t>https://compras.sfiemt.ind.br/Default.aspx</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Diário Oficial (Alvarás Cuiabá/VG)</t>
+          <t>🏢 Sistema S</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Sistema S (Sesi/Senai/Sesc/Sebrae)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SESC MT - SERVIÇO SOCIAL DO COMÉRCIO</t>
+          <t>Reforma / Adequação Predial</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -854,59 +869,60 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Manutenção Predial</t>
-        </is>
+      <c r="D8" t="n">
+        <v>232537.5</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pregão Presencial Sistema S</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>320000</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
+          <t>Alvará de Obra Privada (Adaptação de Ponto Comercial para Drogaria)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>PG-SESC-2026/008</t>
+          <t>PRIVADO: REDE DROGARIAS CENTRO-OESTE LTDA</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Prestação de serviços contínuos de manutenção predial preventiva e corretiva civil, hidráulica e pintura para o complexo cultural do SESC Arsenal em Cuiabá.</t>
+          <t>[Bairro Bosque da Saúde] Reforma e adequação de imóvel comercial com execução de piso porcelanato, forro gesso, fachada em ACM e climatização. Área: 195,00 m². Local: Av. Aclimação, Cuiabá-MT.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>https://transparencia-mt.sesc.com.br</t>
+          <t>ALV-CBA-2026/1650</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>🏢 Sistema S</t>
+          <t>https://gazetamunicipal.cuiaba.mt.gov.br/</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Sistema S (Sesi/Senai/Sesc/Sebrae)</t>
+          <t>🏗️ Obra Privada (Alvará)</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Diário Oficial (Alvarás Cuiabá/VG)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PRIVADO: AUTO POSTO &amp; CONVENIÊNCIA RODOVIA LTDA</t>
+          <t>Manutenção Predial</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>VÁRZEA GRANDE</t>
+          <t>CUIABÁ</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -914,174 +930,177 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Pavimentação / Infraestrutura</t>
-        </is>
+      <c r="D9" t="n">
+        <v>320000</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Alvará de Obra Privada (Pavimentação Rígida e Pista de Abastecimento)</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>4240000</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
+          <t>Pregão Presencial Sistema S</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>ALV-VG-2026/0820</t>
+          <t>SESC MT - SERVIÇO SOCIAL DO COMÉRCIO</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>[Rodovia Mario Andreazza] Execução de pátio em concreto armado usinado, drenagem superficial e muretas de contenção para novo posto de combustíveis. Área: 1.600,00 m². Local: Rodovia Mario Andreazza, VG.</t>
+          <t>Prestação de serviços contínuos de manutenção predial preventiva e corretiva civil, hidráulica e pintura para o complexo cultural do SESC Arsenal em Cuiabá.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>https://diariomunicipal.org/mt/amm/</t>
+          <t>PG-SESC-2026/008</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>🏗️ Obra Privada (Alvará)</t>
+          <t>https://transparencia-mt.sesc.com.br</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Diário Oficial (Alvarás Cuiabá/VG)</t>
+          <t>🏢 Sistema S</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Sistema S (Sesi/Senai/Sesc/Sebrae)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SENAI MT - SERVIÇO NACIONAL DE APRENDIZAGEM INDUSTRIAL</t>
+          <t>Pavimentação / Infraestrutura</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RONDONÓPOLIS</t>
+          <t>VÁRZEA GRANDE</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Construção Civil</t>
-        </is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>4240000</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Concorrência Sistema S</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>890000</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
+          <t>Alvará de Obra Privada (Pavimentação Rígida e Pista de Abastecimento)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>LIC-SENAI-2026/031</t>
+          <t>PRIVADO: AUTO POSTO &amp; CONVENIÊNCIA RODOVIA LTDA</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Construção de galpão anexo em estrutura pré-moldada de concreto e piso industrial para ampliação da oficina de maquinários pesados da Unidade Integrada SENAI Rondonópolis.</t>
+          <t>[Rodovia Mario Andreazza] Execução de pátio em concreto armado usinado, drenagem superficial e muretas de contenção para novo posto de combustíveis. Área: 1.600,00 m². Local: Rodovia Mario Andreazza, VG.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>https://compras.sfiemt.ind.br/Default.aspx</t>
+          <t>ALV-VG-2026/0820</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>🏢 Sistema S</t>
+          <t>https://diariomunicipal.org/mt/amm/</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Sistema S (Sesi/Senai/Sesc/Sebrae)</t>
+          <t>🏗️ Obra Privada (Alvará)</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Diário Oficial (Alvarás Cuiabá/VG)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PRIVADO: CONDOMÍNIO RESIDENCIAL JARDIM CUIABÁ</t>
+          <t>Construção Civil</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CUIABÁ</t>
+          <t>RONDONÓPOLIS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Manutenção Predial</t>
-        </is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>890000</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Alvará de Obra Privada (Reforma de Guarita e Revitalização de Fachada)</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>371000</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
+          <t>Concorrência Sistema S</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>ALV-CBA-2026/1420</t>
+          <t>SENAI MT - SERVIÇO NACIONAL DE APRENDIZAGEM INDUSTRIAL</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>[Jardim Cuiabá] Reforma geral da portaria social, cobertura metálica de acesso e impermeabilização de calhas do condomínio. Local: Bairro Jardim Cuiabá, Cuiabá-MT.</t>
+          <t>Construção de galpão anexo em estrutura pré-moldada de concreto e piso industrial para ampliação da oficina de maquinários pesados da Unidade Integrada SENAI Rondonópolis.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>https://gazetamunicipal.cuiaba.mt.gov.br/</t>
+          <t>LIC-SENAI-2026/031</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>🏗️ Obra Privada (Alvará)</t>
+          <t>https://compras.sfiemt.ind.br/Default.aspx</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Diário Oficial (Alvarás Cuiabá/VG)</t>
+          <t>🏢 Sistema S</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Sistema S (Sesi/Senai/Sesc/Sebrae)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SEBRAE MT</t>
+          <t>Manutenção Predial</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1094,105 +1113,168 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Reforma / Adequação Predial</t>
-        </is>
+      <c r="D12" t="n">
+        <v>371000</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cotação Eletrônica Sistema S</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>95600</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
+          <t>Alvará de Obra Privada (Reforma de Guarita e Revitalização de Fachada)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>COT-SEBRAE-2026/015</t>
+          <t>PRIVADO: CONDOMÍNIO RESIDENCIAL JARDIM CUIABÁ</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Reforma e modernização dos banheiros acessíveis e salas de atendimento do edifício sede do SEBRAE Mato Grosso (Av. CPA, Cuiabá).</t>
+          <t>[Jardim Cuiabá] Reforma geral da portaria social, cobertura metálica de acesso e impermeabilização de calhas do condomínio. Local: Bairro Jardim Cuiabá, Cuiabá-MT.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://sebrae.com.br/sites/PortalSebrae/licitacoes</t>
+          <t>ALV-CBA-2026/1420</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>🏢 Sistema S</t>
+          <t>https://gazetamunicipal.cuiaba.mt.gov.br/</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Sistema S (Sesi/Senai/Sesc/Sebrae)</t>
+          <t>🏗️ Obra Privada (Alvará)</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Diário Oficial (Alvarás Cuiabá/VG)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Reforma / Adequação Predial</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CUIABÁ</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>95600</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Cotação Eletrônica Sistema S</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>SEBRAE MT</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Reforma e modernização dos banheiros acessíveis e salas de atendimento do edifício sede do SEBRAE Mato Grosso (Av. CPA, Cuiabá).</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>COT-SEBRAE-2026/015</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>https://sebrae.com.br/sites/PortalSebrae/licitacoes</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>🏢 Sistema S</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Sistema S (Sesi/Senai/Sesc/Sebrae)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Instalações / Climatização</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>BARÃO DE MELGAÇO</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>540000</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Concorrência Sistema S</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
           <t>SESC MT - SERVIÇO SOCIAL DO COMÉRCIO</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>BARÃO DE MELGAÇO</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Instalações / Climatização</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Concorrência Sistema S</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>540000</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Adequação das instalações elétricas, cabeamento estruturado e instalação de usina solar fotovoltaica no Sesc Pantanal Hotel Poconé/Barão de Melgaço.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
         <is>
           <t>LIC-SESC-2026/027</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Adequação das instalações elétricas, cabeamento estruturado e instalação de usina solar fotovoltaica no Sesc Pantanal Hotel Poconé/Barão de Melgaço.</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>https://transparencia-mt.sesc.com.br</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>🏢 Sistema S</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>Sistema S (Sesi/Senai/Sesc/Sebrae)</t>
         </is>

--- a/oportunidades_obras_mt.xlsx
+++ b/oportunidades_obras_mt.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,16 +491,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CAMPO VERDE</t>
+          <t>CUIABÁ</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>100815</v>
+        <v>40608</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -509,32 +509,32 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-28 08:00</t>
+          <t>2026-09-28 12:00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>INSTITUTO FEDERAL DE EDUCACAO, CIENCIA E TECNOLOGIA DE MATO GROSSO</t>
+          <t>COMANDO DO EXERCITO</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Contratação de serviço de engenharia de adequação de projeto, conforme condições e exigências estabelecidas no termo de referência</t>
+          <t>Contratação de empresa para execução de serviços de engenharia de interligação esgotamento sanitário de 09 (nove) Próprios Nacionais Residenciais (PNR) da Vila Militar Cel Iporã à rede municipal da concessionária Águas Cuiabá.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>23879.000505.2026-98</t>
+          <t>64310.011040/2026-11</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://pncp.gov.br/app/editais/10784782000150/2026/364</t>
+          <t>https://pncp.gov.br/app/editais/00394452000103/2026/20610</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -551,68 +551,72 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Construção Civil</t>
+          <t>Serviços de Engenharia Geral</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CUIABÁ</t>
+          <t>CAMPO VERDE</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2252500</v>
+        <v>100815</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Alvará de Obra Privada (Galpão Logístico e Escritório Comercial)</t>
+          <t>Dispensa</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-09-28 08:00</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>PRIVADO: AGROPECUÁRIA &amp; LOGÍSTICA PANTANAL LTDA</t>
+          <t>INSTITUTO FEDERAL DE EDUCACAO, CIENCIA E TECNOLOGIA DE MATO GROSSO</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>[Distrito Industrial] Construção de barracão metálico para armazenagem e bloco administrativo de alvenaria. Área total aprovada: 850,00 m². Local: Av. A, Distrito Industrial, Cuiabá-MT.</t>
+          <t>Contratação de serviço de engenharia de adequação de projeto, conforme condições e exigências estabelecidas no termo de referência</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>ALV-CBA-2026/1842</t>
+          <t>23879.000505.2026-98</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>https://gazetamunicipal.cuiaba.mt.gov.br/</t>
+          <t>https://pncp.gov.br/app/editais/10784782000150/2026/364</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>🏗️ Obra Privada (Alvará)</t>
+          <t>🏛️ Governo / PNCP</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Diário Oficial (Alvarás Cuiabá/VG)</t>
+          <t>PNCP / Compras.gov (Governo)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Reforma / Adequação Predial</t>
+          <t>Construção Civil</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -626,32 +630,32 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>381600</v>
+        <v>2252500</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Alvará de Obra Privada (Reforma Comercial com Acréscimo de Área)</t>
+          <t>Alvará de Obra Privada (Galpão Logístico e Escritório Comercial)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>PRIVADO: CLÍNICA INTEGRADA SANTA ROSA EIRELI</t>
+          <t>PRIVADO: AGROPECUÁRIA &amp; LOGÍSTICA PANTANAL LTDA</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>[Bairro Santa Rosa] Reforma comercial com adequação de acessibilidade, consultórios médicos e reforço estrutural. Área total: 320,00 m². Local: Rua das Violetas, Santa Rosa, Cuiabá-MT.</t>
+          <t>[Distrito Industrial] Construção de barracão metálico para armazenagem e bloco administrativo de alvenaria. Área total aprovada: 850,00 m². Local: Av. A, Distrito Industrial, Cuiabá-MT.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>ALV-CBA-2026/1790</t>
+          <t>ALV-CBA-2026/1842</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -673,12 +677,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Construção Civil</t>
+          <t>Reforma / Adequação Predial</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>VÁRZEA GRANDE</t>
+          <t>CUIABÁ</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -687,37 +691,37 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3180000</v>
+        <v>381600</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Alvará de Obra Privada (Construção de Centro de Distribuição)</t>
+          <t>Alvará de Obra Privada (Reforma Comercial com Acréscimo de Área)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>PRIVADO: COMERCIAL DE ALIMENTOS UNIÃO MATOGROSSENSE</t>
+          <t>PRIVADO: CLÍNICA INTEGRADA SANTA ROSA EIRELI</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>[Bairro Cristo Rei] Construção de galpão comercial com piso de alta resistência para atacado e câmara frigorífica. Área aprovada: 1.200,00 m². Local: Av. 31 de Março, Várzea Grande-MT.</t>
+          <t>[Bairro Santa Rosa] Reforma comercial com adequação de acessibilidade, consultórios médicos e reforço estrutural. Área total: 320,00 m². Local: Rua das Violetas, Santa Rosa, Cuiabá-MT.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>ALV-VG-2026/0945</t>
+          <t>ALV-CBA-2026/1790</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://diariomunicipal.org/mt/amm/</t>
+          <t>https://gazetamunicipal.cuiaba.mt.gov.br/</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -734,12 +738,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Reforma / Adequação Predial</t>
+          <t>Construção Civil</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CUIABÁ</t>
+          <t>VÁRZEA GRANDE</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -748,59 +752,59 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>485900</v>
+        <v>3180000</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Concorrência Sistema S</t>
+          <t>Alvará de Obra Privada (Construção de Centro de Distribuição)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>SESI MT - SERVIÇO SOCIAL DA INDÚSTRIA</t>
+          <t>PRIVADO: COMERCIAL DE ALIMENTOS UNIÃO MATOGROSSENSE</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Contratação de empresa de engenharia para execução de obras de reforma da cobertura metálica, impermeabilização de calhas e revitalização da fachada da Unidade SESI Saúde Cuiabá.</t>
+          <t>[Bairro Cristo Rei] Construção de galpão comercial com piso de alta resistência para atacado e câmara frigorífica. Área aprovada: 1.200,00 m². Local: Av. 31 de Março, Várzea Grande-MT.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>LIC-SESI-2026/042</t>
+          <t>ALV-VG-2026/0945</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://compras.sfiemt.ind.br/Default.aspx</t>
+          <t>https://diariomunicipal.org/mt/amm/</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>🏢 Sistema S</t>
+          <t>🏗️ Obra Privada (Alvará)</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Sistema S (Sesi/Senai/Sesc/Sebrae)</t>
+          <t>Diário Oficial (Alvarás Cuiabá/VG)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Instalações / Climatização</t>
+          <t>Reforma / Adequação Predial</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>VÁRZEA GRANDE</t>
+          <t>CUIABÁ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -809,32 +813,32 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>118450</v>
+        <v>485900</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dispensa Eletrônica Sistema S</t>
+          <t>Concorrência Sistema S</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>SENAI MT - SERVIÇO NACIONAL DE APRENDIZAGEM INDUSTRIAL</t>
+          <t>SESI MT - SERVIÇO SOCIAL DA INDÚSTRIA</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Reforma e adequação do sistema de climatização e ventilação mecânica dos laboratórios práticos de mecânica e soldagem da Faculdade de Tecnologia SENAI Várzea Grande.</t>
+          <t>Contratação de empresa de engenharia para execução de obras de reforma da cobertura metálica, impermeabilização de calhas e revitalização da fachada da Unidade SESI Saúde Cuiabá.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>DISP-SENAI-2026/019</t>
+          <t>LIC-SESI-2026/042</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -856,12 +860,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Reforma / Adequação Predial</t>
+          <t>Instalações / Climatização</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CUIABÁ</t>
+          <t>VÁRZEA GRANDE</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,54 +874,54 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>232537.5</v>
+        <v>118450</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Alvará de Obra Privada (Adaptação de Ponto Comercial para Drogaria)</t>
+          <t>Dispensa Eletrônica Sistema S</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>PRIVADO: REDE DROGARIAS CENTRO-OESTE LTDA</t>
+          <t>SENAI MT - SERVIÇO NACIONAL DE APRENDIZAGEM INDUSTRIAL</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>[Bairro Bosque da Saúde] Reforma e adequação de imóvel comercial com execução de piso porcelanato, forro gesso, fachada em ACM e climatização. Área: 195,00 m². Local: Av. Aclimação, Cuiabá-MT.</t>
+          <t>Reforma e adequação do sistema de climatização e ventilação mecânica dos laboratórios práticos de mecânica e soldagem da Faculdade de Tecnologia SENAI Várzea Grande.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>ALV-CBA-2026/1650</t>
+          <t>DISP-SENAI-2026/019</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://gazetamunicipal.cuiaba.mt.gov.br/</t>
+          <t>https://compras.sfiemt.ind.br/Default.aspx</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>🏗️ Obra Privada (Alvará)</t>
+          <t>🏢 Sistema S</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Diário Oficial (Alvarás Cuiabá/VG)</t>
+          <t>Sistema S (Sesi/Senai/Sesc/Sebrae)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Manutenção Predial</t>
+          <t>Reforma / Adequação Predial</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -931,59 +935,59 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>320000</v>
+        <v>232537.5</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Pregão Presencial Sistema S</t>
+          <t>Alvará de Obra Privada (Adaptação de Ponto Comercial para Drogaria)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>SESC MT - SERVIÇO SOCIAL DO COMÉRCIO</t>
+          <t>PRIVADO: REDE DROGARIAS CENTRO-OESTE LTDA</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Prestação de serviços contínuos de manutenção predial preventiva e corretiva civil, hidráulica e pintura para o complexo cultural do SESC Arsenal em Cuiabá.</t>
+          <t>[Bairro Bosque da Saúde] Reforma e adequação de imóvel comercial com execução de piso porcelanato, forro gesso, fachada em ACM e climatização. Área: 195,00 m². Local: Av. Aclimação, Cuiabá-MT.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>PG-SESC-2026/008</t>
+          <t>ALV-CBA-2026/1650</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://transparencia-mt.sesc.com.br</t>
+          <t>https://gazetamunicipal.cuiaba.mt.gov.br/</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>🏢 Sistema S</t>
+          <t>🏗️ Obra Privada (Alvará)</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Sistema S (Sesi/Senai/Sesc/Sebrae)</t>
+          <t>Diário Oficial (Alvarás Cuiabá/VG)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Pavimentação / Infraestrutura</t>
+          <t>Manutenção Predial</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>VÁRZEA GRANDE</t>
+          <t>CUIABÁ</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -992,176 +996,176 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4240000</v>
+        <v>320000</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Alvará de Obra Privada (Pavimentação Rígida e Pista de Abastecimento)</t>
+          <t>Pregão Presencial Sistema S</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>PRIVADO: AUTO POSTO &amp; CONVENIÊNCIA RODOVIA LTDA</t>
+          <t>SESC MT - SERVIÇO SOCIAL DO COMÉRCIO</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>[Rodovia Mario Andreazza] Execução de pátio em concreto armado usinado, drenagem superficial e muretas de contenção para novo posto de combustíveis. Área: 1.600,00 m². Local: Rodovia Mario Andreazza, VG.</t>
+          <t>Prestação de serviços contínuos de manutenção predial preventiva e corretiva civil, hidráulica e pintura para o complexo cultural do SESC Arsenal em Cuiabá.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>ALV-VG-2026/0820</t>
+          <t>PG-SESC-2026/008</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://diariomunicipal.org/mt/amm/</t>
+          <t>https://transparencia-mt.sesc.com.br</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>🏗️ Obra Privada (Alvará)</t>
+          <t>🏢 Sistema S</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Diário Oficial (Alvarás Cuiabá/VG)</t>
+          <t>Sistema S (Sesi/Senai/Sesc/Sebrae)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Construção Civil</t>
+          <t>Pavimentação / Infraestrutura</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>RONDONÓPOLIS</t>
+          <t>VÁRZEA GRANDE</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>890000</v>
+        <v>4240000</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Concorrência Sistema S</t>
+          <t>Alvará de Obra Privada (Pavimentação Rígida e Pista de Abastecimento)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>SENAI MT - SERVIÇO NACIONAL DE APRENDIZAGEM INDUSTRIAL</t>
+          <t>PRIVADO: AUTO POSTO &amp; CONVENIÊNCIA RODOVIA LTDA</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Construção de galpão anexo em estrutura pré-moldada de concreto e piso industrial para ampliação da oficina de maquinários pesados da Unidade Integrada SENAI Rondonópolis.</t>
+          <t>[Rodovia Mario Andreazza] Execução de pátio em concreto armado usinado, drenagem superficial e muretas de contenção para novo posto de combustíveis. Área: 1.600,00 m². Local: Rodovia Mario Andreazza, VG.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>LIC-SENAI-2026/031</t>
+          <t>ALV-VG-2026/0820</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://compras.sfiemt.ind.br/Default.aspx</t>
+          <t>https://diariomunicipal.org/mt/amm/</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>🏢 Sistema S</t>
+          <t>🏗️ Obra Privada (Alvará)</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Sistema S (Sesi/Senai/Sesc/Sebrae)</t>
+          <t>Diário Oficial (Alvarás Cuiabá/VG)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Manutenção Predial</t>
+          <t>Construção Civil</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CUIABÁ</t>
+          <t>RONDONÓPOLIS</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>371000</v>
+        <v>890000</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Alvará de Obra Privada (Reforma de Guarita e Revitalização de Fachada)</t>
+          <t>Concorrência Sistema S</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>PRIVADO: CONDOMÍNIO RESIDENCIAL JARDIM CUIABÁ</t>
+          <t>SENAI MT - SERVIÇO NACIONAL DE APRENDIZAGEM INDUSTRIAL</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>[Jardim Cuiabá] Reforma geral da portaria social, cobertura metálica de acesso e impermeabilização de calhas do condomínio. Local: Bairro Jardim Cuiabá, Cuiabá-MT.</t>
+          <t>Construção de galpão anexo em estrutura pré-moldada de concreto e piso industrial para ampliação da oficina de maquinários pesados da Unidade Integrada SENAI Rondonópolis.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>ALV-CBA-2026/1420</t>
+          <t>LIC-SENAI-2026/031</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://gazetamunicipal.cuiaba.mt.gov.br/</t>
+          <t>https://compras.sfiemt.ind.br/Default.aspx</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>🏗️ Obra Privada (Alvará)</t>
+          <t>🏢 Sistema S</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Diário Oficial (Alvarás Cuiabá/VG)</t>
+          <t>Sistema S (Sesi/Senai/Sesc/Sebrae)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Reforma / Adequação Predial</t>
+          <t>Manutenção Predial</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1175,106 +1179,167 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>95600</v>
+        <v>371000</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cotação Eletrônica Sistema S</t>
+          <t>Alvará de Obra Privada (Reforma de Guarita e Revitalização de Fachada)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>SEBRAE MT</t>
+          <t>PRIVADO: CONDOMÍNIO RESIDENCIAL JARDIM CUIABÁ</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Reforma e modernização dos banheiros acessíveis e salas de atendimento do edifício sede do SEBRAE Mato Grosso (Av. CPA, Cuiabá).</t>
+          <t>[Jardim Cuiabá] Reforma geral da portaria social, cobertura metálica de acesso e impermeabilização de calhas do condomínio. Local: Bairro Jardim Cuiabá, Cuiabá-MT.</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>COT-SEBRAE-2026/015</t>
+          <t>ALV-CBA-2026/1420</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://sebrae.com.br/sites/PortalSebrae/licitacoes</t>
+          <t>https://gazetamunicipal.cuiaba.mt.gov.br/</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>🏢 Sistema S</t>
+          <t>🏗️ Obra Privada (Alvará)</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Sistema S (Sesi/Senai/Sesc/Sebrae)</t>
+          <t>Diário Oficial (Alvarás Cuiabá/VG)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Instalações / Climatização</t>
+          <t>Reforma / Adequação Predial</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BARÃO DE MELGAÇO</t>
+          <t>CUIABÁ</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>540000</v>
+        <v>95600</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Concorrência Sistema S</t>
+          <t>Cotação Eletrônica Sistema S</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
+          <t>SEBRAE MT</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Reforma e modernização dos banheiros acessíveis e salas de atendimento do edifício sede do SEBRAE Mato Grosso (Av. CPA, Cuiabá).</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>COT-SEBRAE-2026/015</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>https://sebrae.com.br/sites/PortalSebrae/licitacoes</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>🏢 Sistema S</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Sistema S (Sesi/Senai/Sesc/Sebrae)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Instalações / Climatização</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>BARÃO DE MELGAÇO</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>540000</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Concorrência Sistema S</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
           <t>SESC MT - SERVIÇO SOCIAL DO COMÉRCIO</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>Adequação das instalações elétricas, cabeamento estruturado e instalação de usina solar fotovoltaica no Sesc Pantanal Hotel Poconé/Barão de Melgaço.</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>LIC-SESC-2026/027</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>https://transparencia-mt.sesc.com.br</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>🏢 Sistema S</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>Sistema S (Sesi/Senai/Sesc/Sebrae)</t>
         </is>

--- a/oportunidades_obras_mt.xlsx
+++ b/oportunidades_obras_mt.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -551,72 +551,68 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Serviços de Engenharia Geral</t>
+          <t>Construção Civil</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CAMPO VERDE</t>
+          <t>CUIABÁ</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>100815</v>
+        <v>2252500</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Dispensa</t>
+          <t>Alvará de Obra Privada (Galpão Logístico e Escritório Comercial)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>2026-09-28 08:00</t>
-        </is>
-      </c>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>INSTITUTO FEDERAL DE EDUCACAO, CIENCIA E TECNOLOGIA DE MATO GROSSO</t>
+          <t>PRIVADO: AGROPECUÁRIA &amp; LOGÍSTICA PANTANAL LTDA</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Contratação de serviço de engenharia de adequação de projeto, conforme condições e exigências estabelecidas no termo de referência</t>
+          <t>[Distrito Industrial] Construção de barracão metálico para armazenagem e bloco administrativo de alvenaria. Área total aprovada: 850,00 m². Local: Av. A, Distrito Industrial, Cuiabá-MT.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>23879.000505.2026-98</t>
+          <t>ALV-CBA-2026/1842</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>https://pncp.gov.br/app/editais/10784782000150/2026/364</t>
+          <t>https://gazetamunicipal.cuiaba.mt.gov.br/</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>🏛️ Governo / PNCP</t>
+          <t>🏗️ Obra Privada (Alvará)</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>PNCP / Compras.gov (Governo)</t>
+          <t>Diário Oficial (Alvarás Cuiabá/VG)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Construção Civil</t>
+          <t>Reforma / Adequação Predial</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -630,32 +626,32 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2252500</v>
+        <v>381600</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Alvará de Obra Privada (Galpão Logístico e Escritório Comercial)</t>
+          <t>Alvará de Obra Privada (Reforma Comercial com Acréscimo de Área)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>PRIVADO: AGROPECUÁRIA &amp; LOGÍSTICA PANTANAL LTDA</t>
+          <t>PRIVADO: CLÍNICA INTEGRADA SANTA ROSA EIRELI</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>[Distrito Industrial] Construção de barracão metálico para armazenagem e bloco administrativo de alvenaria. Área total aprovada: 850,00 m². Local: Av. A, Distrito Industrial, Cuiabá-MT.</t>
+          <t>[Bairro Santa Rosa] Reforma comercial com adequação de acessibilidade, consultórios médicos e reforço estrutural. Área total: 320,00 m². Local: Rua das Violetas, Santa Rosa, Cuiabá-MT.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>ALV-CBA-2026/1842</t>
+          <t>ALV-CBA-2026/1790</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -677,12 +673,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Reforma / Adequação Predial</t>
+          <t>Construção Civil</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CUIABÁ</t>
+          <t>VÁRZEA GRANDE</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -691,37 +687,37 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>381600</v>
+        <v>3180000</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Alvará de Obra Privada (Reforma Comercial com Acréscimo de Área)</t>
+          <t>Alvará de Obra Privada (Construção de Centro de Distribuição)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>PRIVADO: CLÍNICA INTEGRADA SANTA ROSA EIRELI</t>
+          <t>PRIVADO: COMERCIAL DE ALIMENTOS UNIÃO MATOGROSSENSE</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>[Bairro Santa Rosa] Reforma comercial com adequação de acessibilidade, consultórios médicos e reforço estrutural. Área total: 320,00 m². Local: Rua das Violetas, Santa Rosa, Cuiabá-MT.</t>
+          <t>[Bairro Cristo Rei] Construção de galpão comercial com piso de alta resistência para atacado e câmara frigorífica. Área aprovada: 1.200,00 m². Local: Av. 31 de Março, Várzea Grande-MT.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>ALV-CBA-2026/1790</t>
+          <t>ALV-VG-2026/0945</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://gazetamunicipal.cuiaba.mt.gov.br/</t>
+          <t>https://diariomunicipal.org/mt/amm/</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -738,12 +734,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Construção Civil</t>
+          <t>Reforma / Adequação Predial</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>VÁRZEA GRANDE</t>
+          <t>CUIABÁ</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -752,59 +748,59 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3180000</v>
+        <v>485900</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Alvará de Obra Privada (Construção de Centro de Distribuição)</t>
+          <t>Concorrência Sistema S</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>PRIVADO: COMERCIAL DE ALIMENTOS UNIÃO MATOGROSSENSE</t>
+          <t>SESI MT - SERVIÇO SOCIAL DA INDÚSTRIA</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>[Bairro Cristo Rei] Construção de galpão comercial com piso de alta resistência para atacado e câmara frigorífica. Área aprovada: 1.200,00 m². Local: Av. 31 de Março, Várzea Grande-MT.</t>
+          <t>Contratação de empresa de engenharia para execução de obras de reforma da cobertura metálica, impermeabilização de calhas e revitalização da fachada da Unidade SESI Saúde Cuiabá.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>ALV-VG-2026/0945</t>
+          <t>LIC-SESI-2026/042</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://diariomunicipal.org/mt/amm/</t>
+          <t>https://compras.sfiemt.ind.br/Default.aspx</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>🏗️ Obra Privada (Alvará)</t>
+          <t>🏢 Sistema S</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Diário Oficial (Alvarás Cuiabá/VG)</t>
+          <t>Sistema S (Sesi/Senai/Sesc/Sebrae)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Reforma / Adequação Predial</t>
+          <t>Instalações / Climatização</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CUIABÁ</t>
+          <t>VÁRZEA GRANDE</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -813,32 +809,32 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>485900</v>
+        <v>118450</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Concorrência Sistema S</t>
+          <t>Dispensa Eletrônica Sistema S</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>SESI MT - SERVIÇO SOCIAL DA INDÚSTRIA</t>
+          <t>SENAI MT - SERVIÇO NACIONAL DE APRENDIZAGEM INDUSTRIAL</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Contratação de empresa de engenharia para execução de obras de reforma da cobertura metálica, impermeabilização de calhas e revitalização da fachada da Unidade SESI Saúde Cuiabá.</t>
+          <t>Reforma e adequação do sistema de climatização e ventilação mecânica dos laboratórios práticos de mecânica e soldagem da Faculdade de Tecnologia SENAI Várzea Grande.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>LIC-SESI-2026/042</t>
+          <t>DISP-SENAI-2026/019</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -860,12 +856,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Instalações / Climatização</t>
+          <t>Reforma / Adequação Predial</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>VÁRZEA GRANDE</t>
+          <t>CUIABÁ</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -874,54 +870,54 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>118450</v>
+        <v>232537.5</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dispensa Eletrônica Sistema S</t>
+          <t>Alvará de Obra Privada (Adaptação de Ponto Comercial para Drogaria)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>SENAI MT - SERVIÇO NACIONAL DE APRENDIZAGEM INDUSTRIAL</t>
+          <t>PRIVADO: REDE DROGARIAS CENTRO-OESTE LTDA</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Reforma e adequação do sistema de climatização e ventilação mecânica dos laboratórios práticos de mecânica e soldagem da Faculdade de Tecnologia SENAI Várzea Grande.</t>
+          <t>[Bairro Bosque da Saúde] Reforma e adequação de imóvel comercial com execução de piso porcelanato, forro gesso, fachada em ACM e climatização. Área: 195,00 m². Local: Av. Aclimação, Cuiabá-MT.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>DISP-SENAI-2026/019</t>
+          <t>ALV-CBA-2026/1650</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://compras.sfiemt.ind.br/Default.aspx</t>
+          <t>https://gazetamunicipal.cuiaba.mt.gov.br/</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>🏢 Sistema S</t>
+          <t>🏗️ Obra Privada (Alvará)</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Sistema S (Sesi/Senai/Sesc/Sebrae)</t>
+          <t>Diário Oficial (Alvarás Cuiabá/VG)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Reforma / Adequação Predial</t>
+          <t>Manutenção Predial</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -935,59 +931,59 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>232537.5</v>
+        <v>320000</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Alvará de Obra Privada (Adaptação de Ponto Comercial para Drogaria)</t>
+          <t>Pregão Presencial Sistema S</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>PRIVADO: REDE DROGARIAS CENTRO-OESTE LTDA</t>
+          <t>SESC MT - SERVIÇO SOCIAL DO COMÉRCIO</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>[Bairro Bosque da Saúde] Reforma e adequação de imóvel comercial com execução de piso porcelanato, forro gesso, fachada em ACM e climatização. Área: 195,00 m². Local: Av. Aclimação, Cuiabá-MT.</t>
+          <t>Prestação de serviços contínuos de manutenção predial preventiva e corretiva civil, hidráulica e pintura para o complexo cultural do SESC Arsenal em Cuiabá.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>ALV-CBA-2026/1650</t>
+          <t>PG-SESC-2026/008</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://gazetamunicipal.cuiaba.mt.gov.br/</t>
+          <t>https://transparencia-mt.sesc.com.br</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>🏗️ Obra Privada (Alvará)</t>
+          <t>🏢 Sistema S</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Diário Oficial (Alvarás Cuiabá/VG)</t>
+          <t>Sistema S (Sesi/Senai/Sesc/Sebrae)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Manutenção Predial</t>
+          <t>Pavimentação / Infraestrutura</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CUIABÁ</t>
+          <t>VÁRZEA GRANDE</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -996,176 +992,176 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>320000</v>
+        <v>4240000</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pregão Presencial Sistema S</t>
+          <t>Alvará de Obra Privada (Pavimentação Rígida e Pista de Abastecimento)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>SESC MT - SERVIÇO SOCIAL DO COMÉRCIO</t>
+          <t>PRIVADO: AUTO POSTO &amp; CONVENIÊNCIA RODOVIA LTDA</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Prestação de serviços contínuos de manutenção predial preventiva e corretiva civil, hidráulica e pintura para o complexo cultural do SESC Arsenal em Cuiabá.</t>
+          <t>[Rodovia Mario Andreazza] Execução de pátio em concreto armado usinado, drenagem superficial e muretas de contenção para novo posto de combustíveis. Área: 1.600,00 m². Local: Rodovia Mario Andreazza, VG.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>PG-SESC-2026/008</t>
+          <t>ALV-VG-2026/0820</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://transparencia-mt.sesc.com.br</t>
+          <t>https://diariomunicipal.org/mt/amm/</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>🏢 Sistema S</t>
+          <t>🏗️ Obra Privada (Alvará)</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Sistema S (Sesi/Senai/Sesc/Sebrae)</t>
+          <t>Diário Oficial (Alvarás Cuiabá/VG)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Pavimentação / Infraestrutura</t>
+          <t>Construção Civil</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>VÁRZEA GRANDE</t>
+          <t>RONDONÓPOLIS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4240000</v>
+        <v>890000</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Alvará de Obra Privada (Pavimentação Rígida e Pista de Abastecimento)</t>
+          <t>Concorrência Sistema S</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>PRIVADO: AUTO POSTO &amp; CONVENIÊNCIA RODOVIA LTDA</t>
+          <t>SENAI MT - SERVIÇO NACIONAL DE APRENDIZAGEM INDUSTRIAL</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>[Rodovia Mario Andreazza] Execução de pátio em concreto armado usinado, drenagem superficial e muretas de contenção para novo posto de combustíveis. Área: 1.600,00 m². Local: Rodovia Mario Andreazza, VG.</t>
+          <t>Construção de galpão anexo em estrutura pré-moldada de concreto e piso industrial para ampliação da oficina de maquinários pesados da Unidade Integrada SENAI Rondonópolis.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>ALV-VG-2026/0820</t>
+          <t>LIC-SENAI-2026/031</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://diariomunicipal.org/mt/amm/</t>
+          <t>https://compras.sfiemt.ind.br/Default.aspx</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>🏗️ Obra Privada (Alvará)</t>
+          <t>🏢 Sistema S</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Diário Oficial (Alvarás Cuiabá/VG)</t>
+          <t>Sistema S (Sesi/Senai/Sesc/Sebrae)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Construção Civil</t>
+          <t>Manutenção Predial</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>RONDONÓPOLIS</t>
+          <t>CUIABÁ</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>890000</v>
+        <v>371000</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Concorrência Sistema S</t>
+          <t>Alvará de Obra Privada (Reforma de Guarita e Revitalização de Fachada)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>SENAI MT - SERVIÇO NACIONAL DE APRENDIZAGEM INDUSTRIAL</t>
+          <t>PRIVADO: CONDOMÍNIO RESIDENCIAL JARDIM CUIABÁ</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Construção de galpão anexo em estrutura pré-moldada de concreto e piso industrial para ampliação da oficina de maquinários pesados da Unidade Integrada SENAI Rondonópolis.</t>
+          <t>[Jardim Cuiabá] Reforma geral da portaria social, cobertura metálica de acesso e impermeabilização de calhas do condomínio. Local: Bairro Jardim Cuiabá, Cuiabá-MT.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>LIC-SENAI-2026/031</t>
+          <t>ALV-CBA-2026/1420</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://compras.sfiemt.ind.br/Default.aspx</t>
+          <t>https://gazetamunicipal.cuiaba.mt.gov.br/</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>🏢 Sistema S</t>
+          <t>🏗️ Obra Privada (Alvará)</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Sistema S (Sesi/Senai/Sesc/Sebrae)</t>
+          <t>Diário Oficial (Alvarás Cuiabá/VG)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Manutenção Predial</t>
+          <t>Reforma / Adequação Predial</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1179,98 +1175,98 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>371000</v>
+        <v>95600</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Alvará de Obra Privada (Reforma de Guarita e Revitalização de Fachada)</t>
+          <t>Cotação Eletrônica Sistema S</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>PRIVADO: CONDOMÍNIO RESIDENCIAL JARDIM CUIABÁ</t>
+          <t>SEBRAE MT</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>[Jardim Cuiabá] Reforma geral da portaria social, cobertura metálica de acesso e impermeabilização de calhas do condomínio. Local: Bairro Jardim Cuiabá, Cuiabá-MT.</t>
+          <t>Reforma e modernização dos banheiros acessíveis e salas de atendimento do edifício sede do SEBRAE Mato Grosso (Av. CPA, Cuiabá).</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>ALV-CBA-2026/1420</t>
+          <t>COT-SEBRAE-2026/015</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://gazetamunicipal.cuiaba.mt.gov.br/</t>
+          <t>https://sebrae.com.br/sites/PortalSebrae/licitacoes</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>🏗️ Obra Privada (Alvará)</t>
+          <t>🏢 Sistema S</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Diário Oficial (Alvarás Cuiabá/VG)</t>
+          <t>Sistema S (Sesi/Senai/Sesc/Sebrae)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Reforma / Adequação Predial</t>
+          <t>Instalações / Climatização</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CUIABÁ</t>
+          <t>BARÃO DE MELGAÇO</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>95600</v>
+        <v>540000</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cotação Eletrônica Sistema S</t>
+          <t>Concorrência Sistema S</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>SEBRAE MT</t>
+          <t>SESC MT - SERVIÇO SOCIAL DO COMÉRCIO</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Reforma e modernização dos banheiros acessíveis e salas de atendimento do edifício sede do SEBRAE Mato Grosso (Av. CPA, Cuiabá).</t>
+          <t>Adequação das instalações elétricas, cabeamento estruturado e instalação de usina solar fotovoltaica no Sesc Pantanal Hotel Poconé/Barão de Melgaço.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>COT-SEBRAE-2026/015</t>
+          <t>LIC-SESC-2026/027</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>https://sebrae.com.br/sites/PortalSebrae/licitacoes</t>
+          <t>https://transparencia-mt.sesc.com.br</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1279,67 +1275,6 @@
         </is>
       </c>
       <c r="M14" t="inlineStr">
-        <is>
-          <t>Sistema S (Sesi/Senai/Sesc/Sebrae)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Instalações / Climatização</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>BARÃO DE MELGAÇO</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>540000</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Concorrência Sistema S</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>SESC MT - SERVIÇO SOCIAL DO COMÉRCIO</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Adequação das instalações elétricas, cabeamento estruturado e instalação de usina solar fotovoltaica no Sesc Pantanal Hotel Poconé/Barão de Melgaço.</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>LIC-SESC-2026/027</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>https://transparencia-mt.sesc.com.br</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>🏢 Sistema S</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
         <is>
           <t>Sistema S (Sesi/Senai/Sesc/Sebrae)</t>
         </is>

--- a/oportunidades_obras_mt.xlsx
+++ b/oportunidades_obras_mt.xlsx
@@ -413,48 +413,48 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Órgão</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Município</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Prioritária (Cuiabá/VG)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>Categoria</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Município</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Prioritária (Cuiabá/VG)</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Modalidade</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
         <is>
           <t>Valor Estimado (R$)</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Modalidade</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Data Publicação</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Encerramento Proposta</t>
-        </is>
-      </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Órgão</t>
+          <t>Processo</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
@@ -464,20 +464,15 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Processo</t>
+          <t>Link PNCP</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Link PNCP</t>
+          <t>Origem</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
-        <is>
-          <t>Origem</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
         <is>
           <t>Alimentador</t>
         </is>
@@ -486,7 +481,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Serviços de Engenharia Geral</t>
+          <t>PRIVADO: AGROPECUÁRIA &amp; LOGÍSTICA PANTANAL LTDA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -499,59 +494,54 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>40608</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Construção Civil</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Dispensa</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
+          <t>Alvará de Obra Privada (Galpão Logístico e Escritório Comercial)</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>2252500</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-28 12:00</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>COMANDO DO EXERCITO</t>
+          <t>ALV-CBA-2026/1842</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Contratação de empresa para execução de serviços de engenharia de interligação esgotamento sanitário de 09 (nove) Próprios Nacionais Residenciais (PNR) da Vila Militar Cel Iporã à rede municipal da concessionária Águas Cuiabá.</t>
+          <t>[Distrito Industrial] Construção de barracão metálico para armazenagem e bloco administrativo de alvenaria. Área total aprovada: 850,00 m². Local: Av. A, Distrito Industrial, Cuiabá-MT.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>64310.011040/2026-11</t>
+          <t>https://gazetamunicipal.cuiaba.mt.gov.br/</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://pncp.gov.br/app/editais/00394452000103/2026/20610</t>
+          <t>🏗️ Obra Privada (Alvará)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>🏛️ Governo / PNCP</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>PNCP / Compras.gov (Governo)</t>
+          <t>Diário Oficial (Alvarás Cuiabá/VG)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Construção Civil</t>
+          <t>PRIVADO: CLÍNICA INTEGRADA SANTA ROSA EIRELI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -564,46 +554,45 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>2252500</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Reforma / Adequação Predial</t>
+        </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Alvará de Obra Privada (Galpão Logístico e Escritório Comercial)</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>Alvará de Obra Privada (Reforma Comercial com Acréscimo de Área)</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>381600</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>PRIVADO: AGROPECUÁRIA &amp; LOGÍSTICA PANTANAL LTDA</t>
+          <t>ALV-CBA-2026/1790</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>[Distrito Industrial] Construção de barracão metálico para armazenagem e bloco administrativo de alvenaria. Área total aprovada: 850,00 m². Local: Av. A, Distrito Industrial, Cuiabá-MT.</t>
+          <t>[Bairro Santa Rosa] Reforma comercial com adequação de acessibilidade, consultórios médicos e reforço estrutural. Área total: 320,00 m². Local: Rua das Violetas, Santa Rosa, Cuiabá-MT.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>ALV-CBA-2026/1842</t>
+          <t>https://gazetamunicipal.cuiaba.mt.gov.br/</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>https://gazetamunicipal.cuiaba.mt.gov.br/</t>
+          <t>🏗️ Obra Privada (Alvará)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
-        <is>
-          <t>🏗️ Obra Privada (Alvará)</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
         <is>
           <t>Diário Oficial (Alvarás Cuiabá/VG)</t>
         </is>
@@ -612,12 +601,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Reforma / Adequação Predial</t>
+          <t>PRIVADO: COMERCIAL DE ALIMENTOS UNIÃO MATOGROSSENSE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CUIABÁ</t>
+          <t>VÁRZEA GRANDE</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -625,46 +614,45 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>381600</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Construção Civil</t>
+        </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Alvará de Obra Privada (Reforma Comercial com Acréscimo de Área)</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>Alvará de Obra Privada (Construção de Centro de Distribuição)</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>3180000</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>PRIVADO: CLÍNICA INTEGRADA SANTA ROSA EIRELI</t>
+          <t>ALV-VG-2026/0945</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>[Bairro Santa Rosa] Reforma comercial com adequação de acessibilidade, consultórios médicos e reforço estrutural. Área total: 320,00 m². Local: Rua das Violetas, Santa Rosa, Cuiabá-MT.</t>
+          <t>[Bairro Cristo Rei] Construção de galpão comercial com piso de alta resistência para atacado e câmara frigorífica. Área aprovada: 1.200,00 m². Local: Av. 31 de Março, Várzea Grande-MT.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>ALV-CBA-2026/1790</t>
+          <t>https://diariomunicipal.org/mt/amm/</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://gazetamunicipal.cuiaba.mt.gov.br/</t>
+          <t>🏗️ Obra Privada (Alvará)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
-        <is>
-          <t>🏗️ Obra Privada (Alvará)</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
         <is>
           <t>Diário Oficial (Alvarás Cuiabá/VG)</t>
         </is>
@@ -673,12 +661,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Construção Civil</t>
+          <t>SESI MT - SERVIÇO SOCIAL DA INDÚSTRIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>VÁRZEA GRANDE</t>
+          <t>CUIABÁ</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -686,60 +674,59 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>3180000</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Reforma / Adequação Predial</t>
+        </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Alvará de Obra Privada (Construção de Centro de Distribuição)</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>Concorrência Sistema S</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>485900</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>PRIVADO: COMERCIAL DE ALIMENTOS UNIÃO MATOGROSSENSE</t>
+          <t>LIC-SESI-2026/042</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>[Bairro Cristo Rei] Construção de galpão comercial com piso de alta resistência para atacado e câmara frigorífica. Área aprovada: 1.200,00 m². Local: Av. 31 de Março, Várzea Grande-MT.</t>
+          <t>Contratação de empresa de engenharia para execução de obras de reforma da cobertura metálica, impermeabilização de calhas e revitalização da fachada da Unidade SESI Saúde Cuiabá.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>ALV-VG-2026/0945</t>
+          <t>https://compras.sfiemt.ind.br/Default.aspx</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://diariomunicipal.org/mt/amm/</t>
+          <t>🏢 Sistema S</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>🏗️ Obra Privada (Alvará)</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Diário Oficial (Alvarás Cuiabá/VG)</t>
+          <t>Sistema S (Sesi/Senai/Sesc/Sebrae)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Reforma / Adequação Predial</t>
+          <t>SENAI MT - SERVIÇO NACIONAL DE APRENDIZAGEM INDUSTRIAL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CUIABÁ</t>
+          <t>VÁRZEA GRANDE</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -747,46 +734,45 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>485900</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Instalações / Climatização</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Concorrência Sistema S</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>Dispensa Eletrônica Sistema S</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>118450</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>SESI MT - SERVIÇO SOCIAL DA INDÚSTRIA</t>
+          <t>DISP-SENAI-2026/019</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Contratação de empresa de engenharia para execução de obras de reforma da cobertura metálica, impermeabilização de calhas e revitalização da fachada da Unidade SESI Saúde Cuiabá.</t>
+          <t>Reforma e adequação do sistema de climatização e ventilação mecânica dos laboratórios práticos de mecânica e soldagem da Faculdade de Tecnologia SENAI Várzea Grande.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>LIC-SESI-2026/042</t>
+          <t>https://compras.sfiemt.ind.br/Default.aspx</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://compras.sfiemt.ind.br/Default.aspx</t>
+          <t>🏢 Sistema S</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
-        <is>
-          <t>🏢 Sistema S</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
         <is>
           <t>Sistema S (Sesi/Senai/Sesc/Sebrae)</t>
         </is>
@@ -795,12 +781,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Instalações / Climatização</t>
+          <t>PRIVADO: REDE DROGARIAS CENTRO-OESTE LTDA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>VÁRZEA GRANDE</t>
+          <t>CUIABÁ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -808,55 +794,54 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>118450</v>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Reforma / Adequação Predial</t>
+        </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dispensa Eletrônica Sistema S</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>Alvará de Obra Privada (Adaptação de Ponto Comercial para Drogaria)</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>232537.5</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>SENAI MT - SERVIÇO NACIONAL DE APRENDIZAGEM INDUSTRIAL</t>
+          <t>ALV-CBA-2026/1650</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Reforma e adequação do sistema de climatização e ventilação mecânica dos laboratórios práticos de mecânica e soldagem da Faculdade de Tecnologia SENAI Várzea Grande.</t>
+          <t>[Bairro Bosque da Saúde] Reforma e adequação de imóvel comercial com execução de piso porcelanato, forro gesso, fachada em ACM e climatização. Área: 195,00 m². Local: Av. Aclimação, Cuiabá-MT.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>DISP-SENAI-2026/019</t>
+          <t>https://gazetamunicipal.cuiaba.mt.gov.br/</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://compras.sfiemt.ind.br/Default.aspx</t>
+          <t>🏗️ Obra Privada (Alvará)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>🏢 Sistema S</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Sistema S (Sesi/Senai/Sesc/Sebrae)</t>
+          <t>Diário Oficial (Alvarás Cuiabá/VG)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Reforma / Adequação Predial</t>
+          <t>SESC MT - SERVIÇO SOCIAL DO COMÉRCIO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -869,60 +854,59 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>232537.5</v>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Manutenção Predial</t>
+        </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Alvará de Obra Privada (Adaptação de Ponto Comercial para Drogaria)</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>Pregão Presencial Sistema S</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>320000</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>PRIVADO: REDE DROGARIAS CENTRO-OESTE LTDA</t>
+          <t>PG-SESC-2026/008</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>[Bairro Bosque da Saúde] Reforma e adequação de imóvel comercial com execução de piso porcelanato, forro gesso, fachada em ACM e climatização. Área: 195,00 m². Local: Av. Aclimação, Cuiabá-MT.</t>
+          <t>Prestação de serviços contínuos de manutenção predial preventiva e corretiva civil, hidráulica e pintura para o complexo cultural do SESC Arsenal em Cuiabá.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>ALV-CBA-2026/1650</t>
+          <t>https://transparencia-mt.sesc.com.br</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://gazetamunicipal.cuiaba.mt.gov.br/</t>
+          <t>🏢 Sistema S</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>🏗️ Obra Privada (Alvará)</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Diário Oficial (Alvarás Cuiabá/VG)</t>
+          <t>Sistema S (Sesi/Senai/Sesc/Sebrae)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Manutenção Predial</t>
+          <t>PRIVADO: AUTO POSTO &amp; CONVENIÊNCIA RODOVIA LTDA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CUIABÁ</t>
+          <t>VÁRZEA GRANDE</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -930,177 +914,174 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="D9" t="n">
-        <v>320000</v>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Pavimentação / Infraestrutura</t>
+        </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Pregão Presencial Sistema S</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>Alvará de Obra Privada (Pavimentação Rígida e Pista de Abastecimento)</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>4240000</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>SESC MT - SERVIÇO SOCIAL DO COMÉRCIO</t>
+          <t>ALV-VG-2026/0820</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Prestação de serviços contínuos de manutenção predial preventiva e corretiva civil, hidráulica e pintura para o complexo cultural do SESC Arsenal em Cuiabá.</t>
+          <t>[Rodovia Mario Andreazza] Execução de pátio em concreto armado usinado, drenagem superficial e muretas de contenção para novo posto de combustíveis. Área: 1.600,00 m². Local: Rodovia Mario Andreazza, VG.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>PG-SESC-2026/008</t>
+          <t>https://diariomunicipal.org/mt/amm/</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://transparencia-mt.sesc.com.br</t>
+          <t>🏗️ Obra Privada (Alvará)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>🏢 Sistema S</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Sistema S (Sesi/Senai/Sesc/Sebrae)</t>
+          <t>Diário Oficial (Alvarás Cuiabá/VG)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Pavimentação / Infraestrutura</t>
+          <t>SENAI MT - SERVIÇO NACIONAL DE APRENDIZAGEM INDUSTRIAL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>VÁRZEA GRANDE</t>
+          <t>RONDONÓPOLIS</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>4240000</v>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Construção Civil</t>
+        </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Alvará de Obra Privada (Pavimentação Rígida e Pista de Abastecimento)</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
+          <t>Concorrência Sistema S</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>890000</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>PRIVADO: AUTO POSTO &amp; CONVENIÊNCIA RODOVIA LTDA</t>
+          <t>LIC-SENAI-2026/031</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>[Rodovia Mario Andreazza] Execução de pátio em concreto armado usinado, drenagem superficial e muretas de contenção para novo posto de combustíveis. Área: 1.600,00 m². Local: Rodovia Mario Andreazza, VG.</t>
+          <t>Construção de galpão anexo em estrutura pré-moldada de concreto e piso industrial para ampliação da oficina de maquinários pesados da Unidade Integrada SENAI Rondonópolis.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>ALV-VG-2026/0820</t>
+          <t>https://compras.sfiemt.ind.br/Default.aspx</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://diariomunicipal.org/mt/amm/</t>
+          <t>🏢 Sistema S</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>🏗️ Obra Privada (Alvará)</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>Diário Oficial (Alvarás Cuiabá/VG)</t>
+          <t>Sistema S (Sesi/Senai/Sesc/Sebrae)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Construção Civil</t>
+          <t>PRIVADO: CONDOMÍNIO RESIDENCIAL JARDIM CUIABÁ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>RONDONÓPOLIS</t>
+          <t>CUIABÁ</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>890000</v>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Manutenção Predial</t>
+        </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Concorrência Sistema S</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
+          <t>Alvará de Obra Privada (Reforma de Guarita e Revitalização de Fachada)</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>371000</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>SENAI MT - SERVIÇO NACIONAL DE APRENDIZAGEM INDUSTRIAL</t>
+          <t>ALV-CBA-2026/1420</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Construção de galpão anexo em estrutura pré-moldada de concreto e piso industrial para ampliação da oficina de maquinários pesados da Unidade Integrada SENAI Rondonópolis.</t>
+          <t>[Jardim Cuiabá] Reforma geral da portaria social, cobertura metálica de acesso e impermeabilização de calhas do condomínio. Local: Bairro Jardim Cuiabá, Cuiabá-MT.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>LIC-SENAI-2026/031</t>
+          <t>https://gazetamunicipal.cuiaba.mt.gov.br/</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://compras.sfiemt.ind.br/Default.aspx</t>
+          <t>🏗️ Obra Privada (Alvará)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>🏢 Sistema S</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>Sistema S (Sesi/Senai/Sesc/Sebrae)</t>
+          <t>Diário Oficial (Alvarás Cuiabá/VG)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Manutenção Predial</t>
+          <t>SEBRAE MT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1113,168 +1094,105 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="D12" t="n">
-        <v>371000</v>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Reforma / Adequação Predial</t>
+        </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Alvará de Obra Privada (Reforma de Guarita e Revitalização de Fachada)</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
+          <t>Cotação Eletrônica Sistema S</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>95600</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>PRIVADO: CONDOMÍNIO RESIDENCIAL JARDIM CUIABÁ</t>
+          <t>COT-SEBRAE-2026/015</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>[Jardim Cuiabá] Reforma geral da portaria social, cobertura metálica de acesso e impermeabilização de calhas do condomínio. Local: Bairro Jardim Cuiabá, Cuiabá-MT.</t>
+          <t>Reforma e modernização dos banheiros acessíveis e salas de atendimento do edifício sede do SEBRAE Mato Grosso (Av. CPA, Cuiabá).</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>ALV-CBA-2026/1420</t>
+          <t>https://sebrae.com.br/sites/PortalSebrae/licitacoes</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://gazetamunicipal.cuiaba.mt.gov.br/</t>
+          <t>🏢 Sistema S</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>🏗️ Obra Privada (Alvará)</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Diário Oficial (Alvarás Cuiabá/VG)</t>
+          <t>Sistema S (Sesi/Senai/Sesc/Sebrae)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Reforma / Adequação Predial</t>
+          <t>SESC MT - SERVIÇO SOCIAL DO COMÉRCIO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CUIABÁ</t>
+          <t>BARÃO DE MELGAÇO</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>95600</v>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Instalações / Climatização</t>
+        </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cotação Eletrônica Sistema S</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
+          <t>Concorrência Sistema S</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>540000</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>SEBRAE MT</t>
+          <t>LIC-SESC-2026/027</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Reforma e modernização dos banheiros acessíveis e salas de atendimento do edifício sede do SEBRAE Mato Grosso (Av. CPA, Cuiabá).</t>
+          <t>Adequação das instalações elétricas, cabeamento estruturado e instalação de usina solar fotovoltaica no Sesc Pantanal Hotel Poconé/Barão de Melgaço.</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>COT-SEBRAE-2026/015</t>
+          <t>https://transparencia-mt.sesc.com.br</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://sebrae.com.br/sites/PortalSebrae/licitacoes</t>
+          <t>🏢 Sistema S</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
-        <is>
-          <t>🏢 Sistema S</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Sistema S (Sesi/Senai/Sesc/Sebrae)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Instalações / Climatização</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>BARÃO DE MELGAÇO</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>540000</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Concorrência Sistema S</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>SESC MT - SERVIÇO SOCIAL DO COMÉRCIO</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Adequação das instalações elétricas, cabeamento estruturado e instalação de usina solar fotovoltaica no Sesc Pantanal Hotel Poconé/Barão de Melgaço.</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>LIC-SESC-2026/027</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>https://transparencia-mt.sesc.com.br</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>🏢 Sistema S</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
         <is>
           <t>Sistema S (Sesi/Senai/Sesc/Sebrae)</t>
         </is>
